--- a/r5-ELGA-MOPED-211-use-system-instad-of-url/StructureDefinition-moped-ext-anzahlBeurlaubungen.xlsx
+++ b/r5-ELGA-MOPED-211-use-system-instad-of-url/StructureDefinition-moped-ext-anzahlBeurlaubungen.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T13:11:55+00:00</t>
+    <t>2024-11-13T15:04:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
